--- a/artfynd/A 61481-2021 artfynd.xlsx
+++ b/artfynd/A 61481-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61481-2021 artfynd.xlsx
+++ b/artfynd/A 61481-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55773940</v>
+        <v>55773922</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573226.8215935663</v>
+        <v>573151</v>
       </c>
       <c r="R2" t="n">
-        <v>7017615.760799286</v>
+        <v>7017448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,20 +764,20 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # Populus tremula</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,37 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55773928</v>
+        <v>55773926</v>
       </c>
       <c r="B3" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>2063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573419.838285814</v>
+        <v>573442</v>
       </c>
       <c r="R3" t="n">
-        <v>7017474.295048638</v>
+        <v>7017355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,21 +867,11 @@
           <t>2015-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,6 +884,16 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -921,7 +901,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,12 +926,7 @@
         <v>104427604</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573169.9361146218</v>
+        <v>573169</v>
       </c>
       <c r="R4" t="n">
-        <v>7017540.184384095</v>
+        <v>7017540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,19 +992,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,37 +1021,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104427596</v>
+        <v>104427298</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1097,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573169.9361146218</v>
+        <v>573037</v>
       </c>
       <c r="R5" t="n">
-        <v>7017540.184384095</v>
+        <v>7017482</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,19 +1090,14 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,6 +1121,342 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>55773940</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellan Öster-Vike och Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573227</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7017616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-08-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-08-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104427596</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573169</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7017540</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>55773928</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellan Öster-Vike och Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573420</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7017474</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-08-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61481-2021 artfynd.xlsx
+++ b/artfynd/A 61481-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104427604</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104427298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773940</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104427596</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,8 +1492,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>